--- a/sheets/인생플랜.xlsx
+++ b/sheets/인생플랜.xlsx
@@ -12,17 +12,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이프페이즈" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인당고정비" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7월생존" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통장구조" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="집자금인출" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8월자산분배" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월예산" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투자종목" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세금최적화" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타임라인" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별저축" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입주후저축" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출산시나리오" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용돈" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026급여배분" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통장구조" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="집자금인출" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10월자산분배" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월예산" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="투자종목" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세금최적화" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="타임라인" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별저축" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입주후저축" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출산시나리오" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용돈" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +472,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -483,7 +484,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현철 (연 3,300만)</t>
+          <t>현철 (연 3,300만·2026-05-18 입사·수습 90%)</t>
         </is>
       </c>
     </row>
@@ -495,7 +496,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여친 (연 2,590만)</t>
+          <t>여친 (연 1,661만)</t>
         </is>
       </c>
     </row>
@@ -543,7 +544,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2033~2034 · 입주 후 월 여유 ~62만</t>
+          <t>2033~2034 · 입주 후 월 여유 ~73만</t>
         </is>
       </c>
     </row>
@@ -554,7 +555,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +596,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
     </row>
     <row r="15">
@@ -631,265 +632,484 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>계좌유형</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>계좌명</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>월(원)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>담당</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>종목/상품</t>
-        </is>
-      </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>월납입</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>연한도</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>목적</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>현철-ISA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
+          <t>월세+관리비</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>600000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MMF/예금</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2029 계약금</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>서민형 3년</t>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>→ 고정비 시트</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>주택청약</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현철-청약</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>50000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종합저축</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>청약 순위</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>640만 유지</t>
-        </is>
-      </c>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>연금저축</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현철-연금</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>KT+SKT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36890</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>현철</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>연금저축</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>세액공제</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>비혼 개인</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>현철-집마련</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
+          <t>통신(여친)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>삼성 CMA</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>379236</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>RP이자</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>집값 1순위</t>
-        </is>
-      </c>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>여친-집마련</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
+          <t>교통-현철</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>215600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>토스 파킹</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>948796</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>고금리</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>집값 1순위</t>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K-패스</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현금</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여친-비상</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+          <t>교통-여친</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>77000</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>여친</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>비자·비상</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K-패스</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>고정비</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>138290</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>138,290</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>고정비</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>구독</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>170580</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>고정비</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>장학금 이자</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>고정비</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>카카오 긴급</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>92220</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>고정비</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>건강보험(여친)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>105371</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>식비</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>주간 장보기</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>750000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>공동계좌에서 결제</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>개인 용돈</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>취미·의류 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>개인 용돈</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ISA 서민형</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>예금·MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>집마련 CMA·토스파킹</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1435081</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>각자</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CMA 181,622 + P2-토스파킹 1,303,459</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>연금저축</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>세액공제용</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>비자 비상</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>50000</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>D-10/F-6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>TOPIK6</t>
-        </is>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P2-토스파킹 (집마련과 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>SUM(C2:C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>세후 수입</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4698532</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>잔액</t>
+        </is>
+      </c>
+      <c r="C22">
+        <f>C21-C20</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -903,217 +1123,264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>비혼 기간 · 2인 각각 신고 (합산신고 불가)</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>계좌유형</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>계좌명</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>종목/상품</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>월납입</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>연한도</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>목적</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ISA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>현철-ISA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MMF/예금</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2029 계약금</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>서민형 3년</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>주택청약</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>현철-청약</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>현철</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>메모</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>종합저축</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>청약 순위</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>640만 유지</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>연 소득(만)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2590</v>
+          <t>연금저축</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>현철-연금</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>세전</t>
+          <t>연금저축</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>세액공제</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>비혼 개인</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>연금저축 납입(연)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>현철-집마련</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P1 240~400만 권장</t>
+          <t>삼성 CMA</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>181622</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RP이자</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>집값 1순위</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>연금 세액공제(15%)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>360000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>여친-집마련</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P2 환급효과 미미</t>
+          <t>토스 파킹</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1253459</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>고금리</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>집값 1순위</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ISA 납입</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
+          <t>현금</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>여친-비상</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>세액공제 없음·이자비과세</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>청년도약</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>불가</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>작년(2025) 근로소득 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>체크카드 소득공제</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>생활비·장보기</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>알바급여</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>전통시장·가맹 30% 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>신용카드</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>고정비 일부</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>15% 구간</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>예상 추가 환급(연)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>410,000원</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>~0~10만</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>연말정산</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>혼인 후</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>신혼특공·디딤돌 8,500만 이하</t>
+          <t>비자·비상</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>D-10/F-6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TOPIK6</t>
         </is>
       </c>
     </row>
@@ -1128,164 +1395,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>시기</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>할 일</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>목표 잔고(집자금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026.07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P0 생존</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>현철 월급만·고정비 123만·ISA/연금 보류</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>비혼 기간 · 2인 각각 신고 (합산신고 불가)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026.08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P1 저축전성</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>급여일 자산분배·여가 0</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2027.02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>비자</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>D-10 연장 (TOPIK6)</t>
+          <t>연 소득(만)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1661</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>세전</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2028.H2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>P2 혼인</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>혼인신고·예식·신혼특공</t>
+          <t>연금저축 납입(연)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P1 240~400만 권장</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2029.06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>P3 숨통</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>카카오 상환 끝·월 +92,220</t>
+          <t>연금 세액공제(15%)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>360000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P2 환급효과 미미</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>P3 분양</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>계약금·중도금(집단대출)</t>
+          <t>ISA 납입</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>세액공제 없음·이자비과세</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2031~32</t>
+          <t>청년도약</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P4 입주</t>
+          <t>불가</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>디딤돌 28,000만·여유 ~62만/월</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>작년(2025) 근로소득 없음</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2033~</t>
+          <t>체크카드 소득공제</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P5 안정</t>
+          <t>생활비·장보기</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>용돈·외식 복구·허리띠 풀기</t>
+          <t>알바급여</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>전통시장·가맹 30% 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>신용카드</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>고정비 일부</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>15% 구간</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>예상 추가 환급(연)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>410,000원</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>~0~10만</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>연말정산</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혼인 후</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>신혼특공·디딤돌 8,500만 이하</t>
         </is>
       </c>
     </row>
@@ -1300,605 +1620,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>월차</t>
+          <t>시기</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>년월</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>월저축</t>
+          <t>할 일</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>누적(집자금)</t>
+          <t>목표 잔고(집자금)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026.07</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+          <t>P0 생존</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>현철 월급만·고정비 140만·ISA/연금 보류</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026.08</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1828032</v>
+          <t>P1 저축전성</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>급여일 자산분배·여가 0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2027.02</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3656064</v>
+          <t>비자</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D-10 연장 (TOPIK6)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2028.H2</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5484096</v>
+          <t>P2 혼인</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>혼인신고·예식·신혼특공</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2029.06</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7312128</v>
+          <t>P3 숨통</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>카카오 상환 끝·월 +92,220</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9140160</v>
+          <t>P3 분양</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>계약금·중도금(집단대출)</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2031~32</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D8" t="n">
-        <v>10968192</v>
+          <t>P4 입주</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>디딤돌 28,000만·여유 ~73만/월</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2033~</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12796224</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14624256</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2027-04</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16452288</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2027-05</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>18280320</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2027-06</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D13" t="n">
-        <v>20108352</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2027-07</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D14" t="n">
-        <v>21936384</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2027-08</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D15" t="n">
-        <v>23764416</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2027-09</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D16" t="n">
-        <v>25592448</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2027-10</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D17" t="n">
-        <v>27420480</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2027-11</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D18" t="n">
-        <v>29248512</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2027-12</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D19" t="n">
-        <v>31076544</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2028-01</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D20" t="n">
-        <v>32904576</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2028-02</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D21" t="n">
-        <v>34732608</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2028-03</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D22" t="n">
-        <v>36560640</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2028-04</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D23" t="n">
-        <v>38388672</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2028-05</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D24" t="n">
-        <v>40216704</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2028-06</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D25" t="n">
-        <v>42044736</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2028-07</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D26" t="n">
-        <v>43872768</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2028-08</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D27" t="n">
-        <v>45700800</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2028-09</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D28" t="n">
-        <v>47528832</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2028-10</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D29" t="n">
-        <v>49356864</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2028-11</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D30" t="n">
-        <v>51184896</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2028-12</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D31" t="n">
-        <v>53012928</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2029-01</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D32" t="n">
-        <v>54840960</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2029-02</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D33" t="n">
-        <v>56668992</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2029-03</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D34" t="n">
-        <v>58497024</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2029-04</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D35" t="n">
-        <v>60325056</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2029-05</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D36" t="n">
-        <v>62153088</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2029-06</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1828032</v>
-      </c>
-      <c r="D37" t="n">
-        <v>63981120</v>
+          <t>P5 안정</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>용돈·외식 복구·허리띠 풀기</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1907,6 +1787,618 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>월차</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>년월</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>월저축</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>누적(집자금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1935081</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3870162</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5805243</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7740324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9675405</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11610486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13545567</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15480648</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2027-04</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17415729</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2027-05</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19350810</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21285891</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23220972</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2027-08</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25156053</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2027-09</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D16" t="n">
+        <v>27091134</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2027-10</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D17" t="n">
+        <v>29026215</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2027-11</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D18" t="n">
+        <v>30961296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2027-12</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32896377</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2028-01</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D20" t="n">
+        <v>34831458</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D21" t="n">
+        <v>36766539</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2028-03</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38701620</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2028-04</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D23" t="n">
+        <v>40636701</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2028-05</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D24" t="n">
+        <v>42571782</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2028-06</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D25" t="n">
+        <v>44506863</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2028-07</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46441944</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2028-08</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D27" t="n">
+        <v>48377025</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2028-09</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D28" t="n">
+        <v>50312106</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2028-10</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D29" t="n">
+        <v>52247187</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2028-11</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D30" t="n">
+        <v>54182268</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2028-12</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D31" t="n">
+        <v>56117349</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2029-01</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D32" t="n">
+        <v>58052430</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2029-02</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D33" t="n">
+        <v>59987511</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2029-03</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D34" t="n">
+        <v>61922592</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2029-04</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D35" t="n">
+        <v>63857673</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2029-05</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D36" t="n">
+        <v>65792754</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2029-06</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1935081</v>
+      </c>
+      <c r="D37" t="n">
+        <v>67727835</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1972,10 +2464,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="C6" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1990,10 +2482,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1321968</v>
+        <v>1513451</v>
       </c>
       <c r="C7" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2036,7 +2528,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1328032</v>
+        <v>1435081</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -2111,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,10 +2618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2078032</v>
+        <v>2185081</v>
       </c>
       <c r="C15" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2690,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>228032</v>
+        <v>335081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2330,7 +2822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2458,10 +2950,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="E5" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F5" t="n">
         <v>750000</v>
@@ -2479,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="L5" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2512,10 +3004,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E6" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F6" t="n">
         <v>750000</v>
@@ -2533,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
       <c r="L6" t="n">
-        <v>1637072</v>
+        <v>1768481</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2566,10 +3058,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E7" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F7" t="n">
         <v>900000</v>
@@ -2587,10 +3079,10 @@
         <v>500000</v>
       </c>
       <c r="K7" t="n">
-        <v>337072</v>
+        <v>468481</v>
       </c>
       <c r="L7" t="n">
-        <v>1087072</v>
+        <v>1218481</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2620,10 +3112,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E8" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F8" t="n">
         <v>900000</v>
@@ -2641,10 +3133,10 @@
         <v>700000</v>
       </c>
       <c r="K8" t="n">
-        <v>237072</v>
+        <v>368481</v>
       </c>
       <c r="L8" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2674,10 +3166,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4949401</v>
+        <v>5285209</v>
       </c>
       <c r="E9" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F9" t="n">
         <v>900000</v>
@@ -2695,10 +3187,10 @@
         <v>700000</v>
       </c>
       <c r="K9" t="n">
-        <v>327433</v>
+        <v>471758</v>
       </c>
       <c r="L9" t="n">
-        <v>1077433</v>
+        <v>1221758</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2728,10 +3220,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="E10" t="n">
-        <v>2021968</v>
+        <v>2213451</v>
       </c>
       <c r="F10" t="n">
         <v>900000</v>
@@ -2749,10 +3241,10 @@
         <v>1000000</v>
       </c>
       <c r="K10" t="n">
-        <v>37072</v>
+        <v>168481</v>
       </c>
       <c r="L10" t="n">
-        <v>587072</v>
+        <v>718481</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2811,7 +3303,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4400000</v>
+        <v>4698532</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2820,10 +3312,10 @@
         <v>500000</v>
       </c>
       <c r="E15" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="F15" t="n">
-        <v>1378032</v>
+        <v>1485081</v>
       </c>
     </row>
     <row r="16">
@@ -2833,7 +3325,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4576000</v>
+        <v>4886473</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -2842,10 +3334,10 @@
         <v>500000</v>
       </c>
       <c r="E16" t="n">
-        <v>804032</v>
+        <v>923022</v>
       </c>
       <c r="F16" t="n">
-        <v>1554032</v>
+        <v>1673022</v>
       </c>
     </row>
     <row r="17">
@@ -2855,7 +3347,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4759040</v>
+        <v>5081932</v>
       </c>
       <c r="C17" t="n">
         <v>700000</v>
@@ -2864,10 +3356,10 @@
         <v>400000</v>
       </c>
       <c r="E17" t="n">
-        <v>237072</v>
+        <v>368481</v>
       </c>
       <c r="F17" t="n">
-        <v>887072</v>
+        <v>1018481</v>
       </c>
     </row>
     <row r="18">
@@ -2877,7 +3369,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4949401</v>
+        <v>5285209</v>
       </c>
       <c r="C18" t="n">
         <v>700000</v>
@@ -2886,10 +3378,10 @@
         <v>400000</v>
       </c>
       <c r="E18" t="n">
-        <v>427433</v>
+        <v>571758</v>
       </c>
       <c r="F18" t="n">
-        <v>1077433</v>
+        <v>1221758</v>
       </c>
     </row>
     <row r="19">
@@ -2899,7 +3391,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5147377</v>
+        <v>5496617</v>
       </c>
       <c r="C19" t="n">
         <v>700000</v>
@@ -2908,10 +3400,10 @@
         <v>400000</v>
       </c>
       <c r="E19" t="n">
-        <v>625409</v>
+        <v>783166</v>
       </c>
       <c r="F19" t="n">
-        <v>1275409</v>
+        <v>1433166</v>
       </c>
     </row>
     <row r="20">
@@ -2921,7 +3413,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5353272</v>
+        <v>5716482</v>
       </c>
       <c r="C20" t="n">
         <v>700000</v>
@@ -2930,10 +3422,10 @@
         <v>400000</v>
       </c>
       <c r="E20" t="n">
-        <v>831304</v>
+        <v>1003031</v>
       </c>
       <c r="F20" t="n">
-        <v>1481304</v>
+        <v>1653031</v>
       </c>
     </row>
   </sheetData>
@@ -2941,7 +3433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3235,11 +3727,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28000</v>
+        <v>120000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$20/월</t>
+          <t>Pro+ 12만/월</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3772,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>86488</v>
+        <v>105371</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3291,7 +3783,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[교통] K-패스 청년30%+여유10%</t>
+          <t>[교통] 정가 (요금×출근일)</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3819,7 @@
         <v>3500</v>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <f>B23*C23</f>
@@ -3335,7 +3827,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>왕복 3500</t>
+          <t>월화수토일·왕복 3500</t>
         </is>
       </c>
     </row>
@@ -3357,11 +3849,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>166148</v>
+        <v>215600</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>K-패스 30%+10%</t>
+          <t>왕복 9800×22</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3864,12 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>45852</v>
+        <v>77000</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>왕복 3500×22</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3381,8 +3878,9 @@
           <t>교통 합계</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>212000</v>
+      <c r="D27">
+        <f>D25+D26</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -3492,7 +3990,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>614520</v>
+        <v>102777</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3501,7 +3999,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>고정비 123만·식비 55만·잔액 CMA</t>
+          <t>고정비 140만·식비 55만·여친 소득 0·잔액 CMA</t>
         </is>
       </c>
     </row>
@@ -3531,12 +4029,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>세후 440만 전부 배분·여가 0</t>
+          <t>세후 ~470만 전부 배분·여가 0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>집마련 133만·ISA 50·연금 20·용돈 25만 유지</t>
+          <t>집마련 143만·ISA 50·연금 20·용돈 25만 유지</t>
         </is>
       </c>
     </row>
@@ -3632,7 +4130,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3667,7 +4165,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>628032</v>
+        <v>735081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3725,7 +4223,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>대출 월 1,150,000 · 집마련 저축 중단 · 여유 628,032원/월</t>
+          <t>대출 월 1,150,000 · 집마련 저축 중단 · 여유 735,081원/월</t>
         </is>
       </c>
     </row>
@@ -3773,13 +4271,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월세+관리비 ½</t>
+          <t>월세+전기 ½→공동</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>325000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3789,13 +4291,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>전기 ½</t>
+          <t>식비 몫→공동</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>383250</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3957,7 +4463,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28000</v>
+        <v>120000</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
@@ -4009,11 +4515,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>166148</v>
+        <v>215600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>K-패스</t>
+          <t>정가</t>
         </is>
       </c>
     </row>
@@ -4024,11 +4530,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>844628</v>
+        <v>986080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>파킹 850,000 권장</t>
+          <t>개인고정 상시 661,080 · 공동이체 708,250</t>
         </is>
       </c>
     </row>
@@ -4040,13 +4546,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>월세+관리비 ½</t>
+          <t>월세+전기 ½→공동</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>325000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4056,13 +4566,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>전기 ½</t>
+          <t>식비 몫→공동</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>366750</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4092,7 +4606,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>86488</v>
+        <v>105371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4112,11 +4626,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45852</v>
+        <v>77000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>K-패스</t>
+          <t>월화수토일·정가</t>
         </is>
       </c>
     </row>
@@ -4127,11 +4641,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>477340</v>
+        <v>527371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>파킹 480,000 권장</t>
+          <t>본인고정 252,371 · 동거분담→KB 공동</t>
         </is>
       </c>
     </row>
@@ -4146,169 +4660,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026년 7월 — 현철 월급만 (여친 근무 시작·첫 급여 8월)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+          <t>2026년 7월 — 수습 세후 ~216만 (6월 근무분·5/18 입사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>여친 소득 8월 입금(7/1~ 근무) · 익월 급여 (전월 근무분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>월(원)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>수입</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>현철 세후</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>고정비</t>
+          <t>수입</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>가구 전체 (건보 제외)</t>
+          <t>현철 세후 (수습 90%)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1235480</v>
+        <v>2160857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>여친 미취업</t>
+          <t>정규 ~240만은 10월~</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>식비</t>
+          <t>수입</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>장보기 (축소)</t>
+          <t>여친</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>배달·외식 최소</t>
+          <t>첫 급여 2026-08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>용돈</t>
+          <t>고정비</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>현철</t>
+          <t>가구 (건보 제외·여친 전화·교통 포함)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100000</v>
+        <v>1408080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15→10만</t>
+          <t>소득은 8월~</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>용돈</t>
+          <t>식비</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>여친</t>
+          <t>장보기 (축소)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>KB 공동</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>저축</t>
+          <t>용돈</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISA·연금</t>
+          <t>현철</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8월부터 재개</t>
+          <t>15→10만</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ISA·연금</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8월부터 재개</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>잔액</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>삼성 CMA</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>614520</v>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C12" t="n">
+        <v>102777</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>집마련·비상</t>
         </is>
@@ -4325,387 +4870,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>급여·파킹·고정비·용돈·저축 분리</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>명의</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>금융사</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>월 입금</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>용도</t>
+          <t>2026 급여 입금·자산 배분 (2026-05-18 입사 · 수습 90%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>익월 급여 (전월 근무분)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P1-급여·고정비</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>급여·고정비</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>입금월</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>근무월</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>현철</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KB 주거래</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>급여 입금+FBS·지로·카드 결제·상시 850,000원</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>집마련</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P1-집마련</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>집마련</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>삼성증권 CMA</t>
-        </is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1008399</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>379236</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>RP·MMF 이자·7월 버퍼도 여기</t>
+        <v>1008399</v>
+      </c>
+      <c r="F5" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5/18 입사·일할</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P1-용돈</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>용돈</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>KB 체크/토스</t>
-        </is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2160857</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>개인 소비만</t>
+        <v>2160857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>102777</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>수습 90%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P1-ISA</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>증권 ISA</t>
-        </is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2160857</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2297580</v>
       </c>
       <c r="E7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>집값 2순위·2029 계약금</t>
+        <v>4458437</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1983709</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1233709</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>수습 90% · 여친 첫 급여(2026-08)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P1-연금</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>연금저축</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2344929</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2612933</v>
       </c>
       <c r="E8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>세액공제만·집값 X</t>
+        <v>4957862</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2444411</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1694411</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>수습→정규 전환</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P1-청약</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>기존 청약</t>
-        </is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2400952</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2387681</v>
       </c>
       <c r="E9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>640만 유지</t>
+        <v>4788633</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2275182</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1525182</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>정규 연봉</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P2-급여·고정비</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>급여·고정비</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>알바 급여 은행</t>
-        </is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2400952</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2297580</v>
       </c>
       <c r="E10" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>급여+건보·교통·통신·상시 480,000원</t>
+        <v>4698532</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2185081</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1435081</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>정규 연봉</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P2-집마련</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>집마련</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>토스뱅크 파킹</t>
-        </is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2400952</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2522833</v>
       </c>
       <c r="E11" t="n">
-        <v>948796</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>고금리 파킹·월 자동이체</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P2-용돈</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>용돈</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>토스</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>개인 소비</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P2-비자비상</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>토스 파킹 또는 별도</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>D-10·비상</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>공동-식비</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>생활</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>KB 또는 토스</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>750000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>장보기만</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>급여일 흐름</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>급여=고정비(KB) · 집마련=CMA/파킹 · 용돈·ISA·연금 분리</t>
+        <v>4923785</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2410334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1660334</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>정규 연봉</t>
         </is>
       </c>
     </row>
@@ -4720,182 +5174,590 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>집값 사용</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>조건</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>비고</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>물리 통장 7개 · 역할 슬롯 10개</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>집마련 CMA·파킹</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>✅ 1순위</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>자유·T+0~1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>삼성CMA(현철)+토스파킹(여친)·보통예금 대신</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ISA 서민형</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>✅ 2순위</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>만기 전 원금 인출</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2029 계약금·이자비과세</t>
+          <t>청약 6,400,000원 · 신규 개설 2건</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>급여·고정비 KB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>비상 시만</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>고정비 버퍼 깨지 않게 최후</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>명의</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>금융사</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>담당 역할</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>주택청약 640만</t>
+          <t>공동</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>⚠️ 비권장</t>
+          <t>KB 공동</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인출 가능하나</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>순위·특공 불리</t>
+          <t>월세·전기·장보기 · ★신규 개설</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>연금저축</t>
+          <t>현철</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>△ 최후</t>
+          <t>KB 주거래</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>부분 인출</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>16.5% + 세액공제 환수</t>
+          <t>급여·개인고정비·저축이체</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IRP</t>
+          <t>현철</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>토스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>주택구입 사유</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>미가입</t>
+          <t>용돈</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>~~보통 집마련 통장~~</t>
+          <t>현철</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>❌</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>이자 낮음</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>사용 안 함</t>
+          <t>CMA(집) · ISA · 연금 · IRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기존 청약</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>청약 2만/월</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>알바 급여 은행</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>급여·본인고정비·동거분담→공동</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>토스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>용돈 10만</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>토스뱅크</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>파킹(집+비자) · ★신규 개설</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>★ 신규 개설</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>명의</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>금융사</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>월세·전기·장보기 · 동거분담금 입금</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>공동명의(또는 연동) · 개설 시 둘 다 방문 · 월 지출 ~140만</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>토스뱅크</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>파킹 통장 · 집마련+비자 자동이체 (~132만/월)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ARC·본인 명의 휴대폰 · 개설 후 한도 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>월 이체 상세</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>아래 슬롯별 금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>명의</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>금융사</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>월 입금</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>용도</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>가계공동</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>동거·공동</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>KB 공동</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>월세·전기·장보기 결제 · 상시 1,400,000원 (현철 708,250 + 여친 691,750)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P1-급여</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>급여·개인고정비</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KB 주거래</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2400952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>급여 → 공동 708,250 · 저축 이체 · 개인고정 상시 661,080원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P1-집마련</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>집마련</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>삼성증권 CMA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>181622</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CMA RP·MMF · 7월 버퍼도 여기</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P1-용돈</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>토스</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>개인 소비만</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P1-ISA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>삼성증권 ISA</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>집값 2순위·2029 계약금</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P1-연금</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>삼성증권 연금</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>세액공제만·집값 X</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P1-청약</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>저축</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>현철</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>기존 청약</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>청약 6,400,000원 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P2-급여·본인고정비</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>급여·본인고정비</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>알바 급여 은행</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2297580</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>급여+건보·교통·통신 · 동거분담 691,750원→가계공동 · 상시 252,371원</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P2-토스파킹</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>집마련·비자</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>토스뱅크</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1303459</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>파킹 집마련 1,253,459 + 비자 50,000 · 2031 입주 후 집마련 중단</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P2-용돈</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>토스</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>용돈 전용 · 토스뱅크(파킹)와 분리</t>
         </is>
       </c>
     </row>
@@ -4910,221 +5772,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>2026년 8월~ — 급여일+1 자동이체 (세후 440만)</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>집값 사용</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>집마련 CMA·파킹</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>✅ 1순위</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>자유·T+0~1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>삼성CMA(현철)+토스파킹(여친·비자5만 포함)·보통예금 대신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>목적 계좌</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ISA 서민형</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>✅ 2순위</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>만기 전 원금 인출</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2029 계약금·이자비과세</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>가계 공동계좌</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>급여·고정비 (잔액 유지)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P1/P2-급여·고정비 — 월 85/48만 상시</t>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>비상 시만</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KB 공동 · 월세·식비 버퍼 깨지 않게 최후</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB 주거래(개인)</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>식비(장보기)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>426136</v>
-      </c>
-      <c r="D5" t="n">
-        <v>323864</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>공동-식비</t>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>비상 시만</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>개인 고정비·저축 이체용 · 공동비 섞지 않기</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>주택청약 640만</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>용돈</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P1-용돈 / P2-용돈</t>
+          <t>⚠️ 비권장</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>인출 가능하나</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>순위·특공 불리</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>연금저축</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ISA</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P1-ISA</t>
+          <t>△ 최후</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>부분 인출</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16.5% + 세액공제 환수</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IRP</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>연금저축</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P1-연금</t>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>주택구입 사유</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>삼성증권 보유·월 납입 플랜 외</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>6</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>~~보통 집마련 통장~~</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비자·비상</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P2-비자비상</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>집마련</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>379236</v>
-      </c>
-      <c r="D10" t="n">
-        <v>948796</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>P1-CMA / P2-파킹</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1900000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>가구 합계</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>4400000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>월 저축 합계</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2078032</v>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>이자 낮음</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>사용 안 함</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5138,480 +5984,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>월(원)</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>담당</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>메모</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026년 10월~ — 급여일+1 자동이체 (세후 ~470만·정규)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>고정비</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>월세+관리비</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>→ 고정비 시트</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>전기</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>8~9월은 수습·전환 → 「2026급여배분」 시트 참고</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KT+SKT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>36890</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>현철</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>여친</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>목적 계좌</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>통신(여친)</t>
+          <t>동거 공동계좌</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>708250</v>
+      </c>
+      <c r="D5" t="n">
+        <v>691750</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P1/P2→가계공동 (KB 공동) · 상시 1,400,000원</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>교통-현철</t>
+          <t>용돈</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>166148</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
+        <v>150000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>K-패스</t>
+          <t>토스 / 토스</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
+      <c r="A7" t="n">
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>교통-여친</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45852</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
+        <v>500000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>K-패스</t>
+          <t>삼성증권 ISA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
+      <c r="A8" t="n">
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>연금저축</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>138290</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
+        <v>200000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>138,290</t>
+          <t>삼성증권 연금</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
+      <c r="A9" t="n">
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구독</t>
+          <t>합계</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>78580</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>2400952</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2297580</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>삼성증권 CMA / 토스뱅크 (집 1,253,459+비자 50,000)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
-      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>장학금 이자</t>
+          <t>가구 합계</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>4698532</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>카카오 긴급</t>
+          <t>월 저축 합계</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92220</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>고정비</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>건강보험(여친)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>86488</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>식비</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>주간 장보기</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>배달·외식 거의 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>용돈</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>개인 용돈</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>취미·의류 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>용돈</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>개인 용돈</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ISA 서민형</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>예금·MMF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>집마련 CMA·파킹</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1328032</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>각자</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CMA 379,236 + 파킹 948,796</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>연금저축</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>현철</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>세액공제용</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>저축</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>비자 비상</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>여친</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C20">
-        <f>SUM(C2:C19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>세후 수입</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4400000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>잔액</t>
-        </is>
-      </c>
-      <c r="C22">
-        <f>C21-C20</f>
-        <v/>
+        <v>2185081</v>
       </c>
     </row>
   </sheetData>
